--- a/hanoi_trajectory_gt_confusion.xlsx
+++ b/hanoi_trajectory_gt_confusion.xlsx
@@ -625,7 +625,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>PRECONDITIONS (in prev state)</t>
+          <t>PRECONDITIONS (present in prev state)</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>ADD EFFECTS (in next state)</t>
+          <t>ADD EFFECTS (absent in prev → present in next)</t>
         </is>
       </c>
     </row>
@@ -960,266 +960,266 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>TP=23 FP=0
-FN=13 TN=0</t>
+          <t>TP=14 FP=0
+FN=22 TN=0</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=12 TN=0</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>TP=31 FP=0
+FN=53 TN=0</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>TP=10 FP=0
+FN=66 TN=0</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>TP=6 FP=0
+FN=70 TN=0</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>TP=5 FP=0
+FN=71 TN=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>on-disc(disc,to)</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>TP=2 FP=0
+FN=2 TN=0
+SW=2</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>TP=10 FP=0
+FN=26 TN=0
+SW=13</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>TP=3 FP=0
+FN=9 TN=0
+SW=5</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>TP=6 FP=0
+FN=78 TN=0
+SW=45</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>TP=6 FP=0
+FN=70 TN=0
+SW=29</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>TP=6 FP=0
+FN=70 TN=0
+SW=31</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>TP=2 FP=0
+FN=74 TN=0
+SW=18</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>DELETE EFFECTS (present in prev → absent in next)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>DEL</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>on-disc(disc,from)</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>TP=2 FP=0
+FN=2 TN=0
+SW=2</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>TP=8 FP=0
+FN=28 TN=0
+SW=18</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=11 TN=0
+SW=8</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>TP=14 FP=0
+FN=70 TN=0
+SW=37</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>TP=6 FP=0
+FN=70 TN=0
+SW=26</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>TP=5 FP=0
+FN=71 TN=0
+SW=21</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=75 TN=0
+SW=14</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>DEL</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>clear-disc(to)</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>TP=3 FP=0
+FN=1 TN=0</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>TP=12 FP=0
+FN=24 TN=0</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>TP=6 FP=0
 FN=6 TN=0</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>TP=34 FP=0
-FN=50 TN=0</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>TP=13 FP=0
-FN=63 TN=0</t>
-        </is>
-      </c>
-      <c r="K12" s="7" t="inlineStr">
-        <is>
-          <t>TP=13 FP=0
-FN=63 TN=0</t>
-        </is>
-      </c>
-      <c r="L12" s="7" t="inlineStr">
-        <is>
-          <t>TP=12 FP=0
-FN=64 TN=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>on-disc(disc,to)</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>TP=3 FP=0
-FN=1 TN=0
-SW=1</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>TP=19 FP=0
-FN=17 TN=0
-SW=15</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>TP=5 FP=0
-FN=7 TN=0
-SW=6</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>TP=31 FP=0
-FN=53 TN=0
-SW=51</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>TP=30 FP=0
-FN=46 TN=0
-SW=44</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="inlineStr">
-        <is>
-          <t>TP=29 FP=0
-FN=47 TN=0
-SW=46</t>
-        </is>
-      </c>
-      <c r="L13" s="7" t="inlineStr">
-        <is>
-          <t>TP=34 FP=0
-FN=42 TN=0
-SW=42</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>DELETE EFFECTS (absent from next state)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>DEL</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>on-disc(disc,from)</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=1
-FN=0 TN=3
-SW=1</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=9
-FN=0 TN=27
-SW=9</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=3
-FN=0 TN=9
-SW=3</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=24
-FN=0 TN=60
-SW=24</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=32
-FN=0 TN=44
-SW=32</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=32
-FN=0 TN=44
-SW=32</t>
-        </is>
-      </c>
-      <c r="L16" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=37
-FN=0 TN=39
-SW=37</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>DEL</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>clear-disc(to)</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=4</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=10
-FN=0 TN=26</t>
-        </is>
-      </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=3
-FN=0 TN=9</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=27
-FN=0 TN=57</t>
+FN=71 TN=0</t>
         </is>
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>TP=0 FP=26
-FN=0 TN=50</t>
+          <t>TP=9 FP=0
+FN=67 TN=0</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>TP=0 FP=16
-FN=0 TN=60</t>
+          <t>TP=8 FP=0
+FN=68 TN=0</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>TP=0 FP=11
-FN=0 TN=65</t>
+          <t>TP=10 FP=0
+FN=66 TN=0</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1376,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>PRECONDITIONS (in prev state)</t>
+          <t>PRECONDITIONS (present in prev state)</t>
         </is>
       </c>
     </row>
@@ -1685,7 +1685,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>ADD EFFECTS (in next state)</t>
+          <t>ADD EFFECTS (absent in prev → present in next)</t>
         </is>
       </c>
     </row>
@@ -1706,10 +1706,10 @@
 FN=0 TN=0</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>TP=5 FP=0
-FN=0 TN=0</t>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>TP=4 FP=0
+FN=1 TN=0</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -1755,8 +1755,8 @@
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
-          <t>TP=1 FP=0
-FN=12 TN=0</t>
+          <t>TP=0 FP=0
+FN=13 TN=0</t>
         </is>
       </c>
     </row>
@@ -1829,7 +1829,7 @@
         <is>
           <t>TP=1 FP=0
 FN=12 TN=0
-SW=12</t>
+SW=11</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
@@ -1843,7 +1843,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>DELETE EFFECTS (absent from next state)</t>
+          <t>DELETE EFFECTS (present in prev → absent in next)</t>
         </is>
       </c>
     </row>
@@ -1860,70 +1860,70 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
+          <t>TP=3 FP=0
+FN=0 TN=0
+SW=0</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>TP=3 FP=0
+FN=2 TN=0
+SW=2</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=0 TN=0
+SW=0</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>TP=6 FP=0
+FN=7 TN=0
+SW=2</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>TP=2 FP=0
+FN=7 TN=0
+SW=4</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>TP=5 FP=0
+FN=16 TN=0
+SW=5</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>TP=5 FP=0
+FN=8 TN=0
+SW=1</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>TP=2 FP=0
+FN=11 TN=0
+SW=3</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
           <t>TP=0 FP=0
-FN=0 TN=3
-SW=0</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=5
-SW=0</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=1
-SW=0</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=7
-FN=0 TN=6
-SW=1</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=5
-FN=0 TN=4
-SW=1</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=16
-FN=0 TN=5
-SW=5</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=8
-FN=0 TN=5
-SW=4</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=11
-FN=0 TN=2
-SW=4</t>
-        </is>
-      </c>
-      <c r="L16" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=12
-FN=0 TN=1
-SW=4</t>
+FN=13 TN=0
+SW=3</t>
         </is>
       </c>
     </row>
@@ -1940,20 +1940,20 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
+          <t>TP=3 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=5</t>
+          <t>TP=5 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=1</t>
+          <t>TP=1 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -1963,38 +1963,38 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=13</t>
+          <t>TP=13 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>TP=0 FP=1
-FN=0 TN=8</t>
+          <t>TP=8 FP=0
+FN=1 TN=0</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>TP=0 FP=3
-FN=0 TN=18</t>
+          <t>TP=18 FP=0
+FN=3 TN=0</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=13</t>
-        </is>
-      </c>
-      <c r="K17" s="6" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=13</t>
+          <t>TP=13 FP=0
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>TP=11 FP=0
+FN=2 TN=0</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=13</t>
+          <t>TP=13 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>PRECONDITIONS (in prev state)</t>
+          <t>PRECONDITIONS (present in prev state)</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>ADD EFFECTS (in next state)</t>
+          <t>ADD EFFECTS (absent in prev → present in next)</t>
         </is>
       </c>
     </row>
@@ -2511,10 +2511,10 @@
 FN=0 TN=0</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>TP=9 FP=0
-FN=0 TN=0</t>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>TP=8 FP=0
+FN=1 TN=0</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -2564,7 +2564,7 @@
         <is>
           <t>TP=2 FP=0
 FN=3 TN=0
-SW=2</t>
+SW=3</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -2583,133 +2583,133 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>TP=10 FP=0
-FN=3 TN=0
+          <t>TP=6 FP=0
+FN=7 TN=0
 SW=3</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>TP=8 FP=0
-FN=1 TN=0
+          <t>TP=7 FP=0
+FN=2 TN=0
 SW=1</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>TP=15 FP=0
+          <t>TP=5 FP=0
+FN=16 TN=0
+SW=6</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>TP=5 FP=0
 FN=6 TN=0
-SW=6</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>TP=10 FP=0
-FN=1 TN=0
 SW=1</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>TP=10 FP=0
-FN=1 TN=0
+          <t>TP=1 FP=0
+FN=10 TN=0
+SW=2</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=10 TN=0
 SW=0</t>
         </is>
       </c>
-      <c r="L13" s="6" t="inlineStr">
-        <is>
-          <t>TP=11 FP=0
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>DELETE EFFECTS (present in prev → absent in next)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>DEL</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>on-peg(disc,from)</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>TP=3 FP=0
 FN=0 TN=0
 SW=0</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>DELETE EFFECTS (absent from next state)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>DEL</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>on-peg(disc,from)</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=3
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>TP=3 FP=0
+FN=2 TN=0
+SW=2</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=0 TN=0
 SW=0</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=5
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=0 TN=0
 SW=0</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=1
-SW=0</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=1
-SW=0</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=13
-SW=0</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=9
-SW=0</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=21
-SW=0</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=11
-SW=0</t>
-        </is>
-      </c>
-      <c r="K16" s="6" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=11
-SW=0</t>
-        </is>
-      </c>
-      <c r="L16" s="6" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=11
-SW=0</t>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>TP=6 FP=0
+FN=7 TN=0
+SW=7</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>TP=6 FP=0
+FN=3 TN=0
+SW=2</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>TP=4 FP=0
+FN=17 TN=0
+SW=16</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>TP=3 FP=0
+FN=8 TN=0
+SW=6</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=10 TN=0
+SW=7</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=10 TN=0
+SW=9</t>
         </is>
       </c>
     </row>
@@ -2726,62 +2726,62 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>TP=0 FP=1
-FN=0 TN=2</t>
+          <t>TP=1 FP=0
+FN=2 TN=0</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>TP=0 FP=3
-FN=0 TN=2</t>
+          <t>TP=1 FP=0
+FN=4 TN=0</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
+          <t>TP=1 FP=0
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>TP=5 FP=0
+FN=8 TN=0</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>TP=5 FP=0
+FN=4 TN=0</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>TP=5 FP=0
+FN=16 TN=0</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>TP=3 FP=0
+FN=8 TN=0</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=10 TN=0</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
           <t>TP=0 FP=0
-FN=0 TN=1</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=1</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=3
-FN=0 TN=10</t>
-        </is>
-      </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=1
-FN=0 TN=8</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=6
-FN=0 TN=15</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=1
-FN=0 TN=10</t>
-        </is>
-      </c>
-      <c r="K17" s="6" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=11</t>
-        </is>
-      </c>
-      <c r="L17" s="6" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=11</t>
+FN=11 TN=0</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2938,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>PRECONDITIONS (in prev state)</t>
+          <t>PRECONDITIONS (present in prev state)</t>
         </is>
       </c>
     </row>
@@ -3229,7 +3229,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>ADD EFFECTS (in next state)</t>
+          <t>ADD EFFECTS (absent in prev → present in next)</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>DELETE EFFECTS (absent from next state)</t>
+          <t>DELETE EFFECTS (present in prev → absent in next)</t>
         </is>
       </c>
     </row>
@@ -3395,49 +3395,49 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
+          <t>TP=1 FP=0
+FN=0 TN=0
+SW=0</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=0 TN=0
+SW=0</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=0 TN=0
+SW=0</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=0 TN=0
+SW=0</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=0 TN=0
+SW=0</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
           <t>TP=0 FP=0
-FN=0 TN=1
-SW=0</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=1
-SW=0</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=1
-SW=0</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=1
-SW=0</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=1
-SW=0</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=1
-SW=0</t>
+FN=1 TN=0
+SW=1</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
@@ -3469,20 +3469,20 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=1</t>
+          <t>TP=1 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=1</t>
+          <t>TP=1 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=1</t>
+          <t>TP=1 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -3492,20 +3492,20 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=1</t>
+          <t>TP=1 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=1</t>
+          <t>TP=1 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>TP=0 FP=0
-FN=0 TN=1</t>
+          <t>TP=1 FP=0
+FN=0 TN=0</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
